--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-sujet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5178,7 +5178,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>183</v>
       </c>
@@ -5193,13 +5193,13 @@
         <v>62</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5281,7 +5281,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>186</v>
       </c>
@@ -5296,13 +5296,13 @@
         <v>187</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5590,7 +5590,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>199</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>74</v>
